--- a/ConfigWorkspace/Data/__tables__.xlsx
+++ b/ConfigWorkspace/Data/__tables__.xlsx
@@ -242,16 +242,16 @@
     <t>元素反应规则</t>
   </si>
   <si>
-    <t>demo.TbElementResult</t>
-  </si>
-  <si>
-    <t>ElementResult</t>
-  </si>
-  <si>
-    <t>element_result.xlsx</t>
-  </si>
-  <si>
-    <t>元素反应结果地块</t>
+    <t>demo.TbTileEffect</t>
+  </si>
+  <si>
+    <t>TileEffect</t>
+  </si>
+  <si>
+    <t>tile_effect.xlsx</t>
+  </si>
+  <si>
+    <t>反应效果</t>
   </si>
 </sst>
 </file>

--- a/ConfigWorkspace/Data/__tables__.xlsx
+++ b/ConfigWorkspace/Data/__tables__.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2A3E11-F05D-418F-A6F9-9488AEB5DC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="4110" windowWidth="19785" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="85">
   <si>
     <t>##var</t>
   </si>
@@ -259,34 +261,40 @@
   </si>
   <si>
     <t>dso.TbEnemyDrop</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EnemyDrop</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>enemy_drop.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>敌人掉落物配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dso.TbSlotDialogue</t>
+  </si>
+  <si>
+    <t>SlotDialogue</t>
+  </si>
+  <si>
+    <t>slot_dialogue.xlsx</t>
+  </si>
+  <si>
+    <t>剧情文本表</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,13 +310,144 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,8 +460,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -330,12 +649,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -343,7 +901,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -355,18 +913,61 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -624,14 +1225,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="20.375" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
@@ -640,7 +1241,7 @@
     <col min="6" max="9" width="18" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +1276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -707,7 +1308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" s="1" customFormat="1" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -730,7 +1331,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:9">
       <c r="B4" t="s">
         <v>27</v>
       </c>
@@ -753,7 +1354,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:9">
       <c r="B5" s="3" t="s">
         <v>33</v>
       </c>
@@ -776,7 +1377,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:9">
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
@@ -799,7 +1400,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:9">
       <c r="B7" s="3" t="s">
         <v>41</v>
       </c>
@@ -822,7 +1423,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:9">
       <c r="B8" s="3" t="s">
         <v>45</v>
       </c>
@@ -845,7 +1446,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:9">
       <c r="B9" s="3" t="s">
         <v>49</v>
       </c>
@@ -868,7 +1469,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:9">
       <c r="B10" s="3" t="s">
         <v>53</v>
       </c>
@@ -891,7 +1492,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:9">
       <c r="B11" s="3" t="s">
         <v>57</v>
       </c>
@@ -914,7 +1515,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:9">
       <c r="B12" t="s">
         <v>61</v>
       </c>
@@ -937,7 +1538,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:9">
       <c r="B13" s="5" t="s">
         <v>65</v>
       </c>
@@ -960,7 +1561,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:9">
       <c r="B14" s="5" t="s">
         <v>69</v>
       </c>
@@ -983,7 +1584,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:9">
       <c r="B15" s="5" t="s">
         <v>73</v>
       </c>
@@ -1006,7 +1607,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:9">
       <c r="B16" s="5" t="s">
         <v>77</v>
       </c>
@@ -1020,18 +1621,41 @@
         <v>79</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H16" s="2" t="s">
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>82</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/__tables__.xlsx
+++ b/ConfigWorkspace/Data/__tables__.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461E7D8B-9AF5-4622-9DBB-8F2E0AF29AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4824" yWindow="4224" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="73">
   <si>
     <t>##var</t>
   </si>
@@ -223,34 +225,40 @@
   </si>
   <si>
     <t>dso.TbWaveEnemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>WaveEnemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>wave_enemy.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>波次与敌人对应表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dso.TbLevelWave</t>
+  </si>
+  <si>
+    <t>LevelWave</t>
+  </si>
+  <si>
+    <t>level_wave.xlsx</t>
+  </si>
+  <si>
+    <t>关卡与关卡中各波次对应表</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,21 +274,151 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -293,8 +431,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -302,12 +620,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -315,30 +872,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -596,23 +1196,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="20.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.3333333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.6666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.3333333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.3333333333333" style="2" customWidth="1"/>
     <col min="6" max="9" width="18" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -647,7 +1247,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -679,7 +1279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" s="1" customFormat="1" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -702,7 +1302,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9">
       <c r="B4" t="s">
         <v>27</v>
       </c>
@@ -725,8 +1325,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="2:9">
+      <c r="B5" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C5" t="s">
@@ -748,8 +1348,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+    <row r="6" spans="2:9">
+      <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C6" t="s">
@@ -771,8 +1371,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="2:9">
+      <c r="B7" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C7" t="s">
@@ -794,8 +1394,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+    <row r="8" spans="2:9">
+      <c r="B8" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C8" t="s">
@@ -817,8 +1417,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="2:9">
+      <c r="B9" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C9" t="s">
@@ -840,8 +1440,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+    <row r="10" spans="2:9">
+      <c r="B10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C10" t="s">
@@ -853,7 +1453,7 @@
       <c r="E10" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H10" t="s">
@@ -863,8 +1463,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
+    <row r="11" spans="2:9">
+      <c r="B11" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C11" t="s">
@@ -876,7 +1476,7 @@
       <c r="E11" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H11" t="s">
@@ -886,7 +1486,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9">
       <c r="B12" t="s">
         <v>61</v>
       </c>
@@ -909,7 +1509,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9">
       <c r="B13" s="5" t="s">
         <v>65</v>
       </c>
@@ -923,18 +1523,41 @@
         <v>67</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H13" s="5" t="s">
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="C14" s="2" t="s">
         <v>70</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/__tables__.xlsx
+++ b/ConfigWorkspace/Data/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -246,6 +246,18 @@
   </si>
   <si>
     <t>关卡与关卡中各波次对应表</t>
+  </si>
+  <si>
+    <t>dso.TbAudioMap</t>
+  </si>
+  <si>
+    <t>AudioMap</t>
+  </si>
+  <si>
+    <t>audio_map.xlsx</t>
+  </si>
+  <si>
+    <t>音效类型与对应文件的名称</t>
   </si>
 </sst>
 </file>
@@ -258,7 +270,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,13 +281,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -738,133 +743,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -876,13 +881,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1202,7 +1207,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="20.3333333333333" style="2" customWidth="1"/>
@@ -1555,6 +1560,29 @@
         <v>72</v>
       </c>
     </row>
+    <row r="15" spans="2:9">
+      <c r="B15" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/ConfigWorkspace/Data/__tables__.xlsx
+++ b/ConfigWorkspace/Data/__tables__.xlsx
@@ -1,33 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2A3E11-F05D-418F-A6F9-9488AEB5DC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView xWindow="1380" yWindow="4110" windowWidth="19785" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="83">
   <si>
     <t>##var</t>
   </si>
@@ -258,19 +256,37 @@
   </si>
   <si>
     <t>音效类型与对应文件的名称</t>
+  </si>
+  <si>
+    <t>dso.TbEnemyDrop</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemyDrop</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_drop.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人掉落物配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -286,144 +302,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,188 +321,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -625,251 +330,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -877,7 +343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -889,61 +355,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1201,23 +624,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.3333333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.6666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.3333333333333" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.3333333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.375" style="2" customWidth="1"/>
     <col min="6" max="9" width="18" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1252,7 +675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1284,7 +707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1307,7 +730,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>27</v>
       </c>
@@ -1330,7 +753,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>33</v>
       </c>
@@ -1353,7 +776,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:9">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
@@ -1376,7 +799,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:9">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>41</v>
       </c>
@@ -1399,7 +822,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>45</v>
       </c>
@@ -1422,7 +845,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
         <v>49</v>
       </c>
@@ -1445,7 +868,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
         <v>53</v>
       </c>
@@ -1468,7 +891,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="2:9">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
         <v>57</v>
       </c>
@@ -1491,7 +914,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>61</v>
       </c>
@@ -1514,7 +937,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
         <v>65</v>
       </c>
@@ -1537,7 +960,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>69</v>
       </c>
@@ -1560,7 +983,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="2:9">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="s">
         <v>73</v>
       </c>
@@ -1583,9 +1006,32 @@
         <v>76</v>
       </c>
     </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B16" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>